--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\科研论文_组内\jizuzuhe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBF3AE8-F44E-4437-BBDE-807273208030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844DBCFF-A04F-435B-A19D-3941E9EEBEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{D6F3ABD2-5076-46B5-BA1B-8C7E6BC485EC}"/>
   </bookViews>
@@ -464,14 +464,6 @@
   </si>
   <si>
     <t>Thermal power units</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pmax (p.u.)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pmin (p.u.)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -782,6 +774,56 @@
   </si>
   <si>
     <t>$4/(MW/Hz)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>max</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (p.u.)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>min</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (p.u.)</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2184,10 +2226,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2367,7 +2409,7 @@
         <v>35</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="27" x14ac:dyDescent="0.3">
@@ -6648,46 +6690,46 @@
         <v>112</v>
       </c>
       <c r="B107" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D107" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C107" s="5" t="s">
+      <c r="E107" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D107" s="5" t="s">
+      <c r="F107" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="G107" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F107" s="5" t="s">
+      <c r="H107" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="G107" s="5" t="s">
+      <c r="I107" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="H107" s="5" t="s">
+      <c r="J107" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="I107" s="5" t="s">
+      <c r="K107" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="J107" s="5" t="s">
+      <c r="L107" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="K107" s="5" t="s">
+      <c r="M107" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="L107" s="5" t="s">
+      <c r="N107" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="M107" s="5" t="s">
+      <c r="O107" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="N107" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="O107" s="5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.3">
